--- a/Data/ModelResponse/Random/evaluation/evaluation_summary.xlsx
+++ b/Data/ModelResponse/Random/evaluation/evaluation_summary.xlsx
@@ -497,37 +497,37 @@
         <v>19200</v>
       </c>
       <c r="C2" t="n">
-        <v>3162</v>
+        <v>19200</v>
       </c>
       <c r="D2" t="n">
-        <v>16038</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.081875</v>
+        <v>0.49671875</v>
       </c>
       <c r="G2" t="n">
-        <v>0.497346792409279</v>
+        <v>0.4968718729422463</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08181049382600841</v>
+        <v>0.4983850649175061</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1400337184849462</v>
+        <v>0.4285591770044276</v>
       </c>
       <c r="J2" t="n">
-        <v>653</v>
+        <v>8084</v>
       </c>
       <c r="K2" t="n">
-        <v>933</v>
+        <v>1470</v>
       </c>
       <c r="L2" t="n">
-        <v>657</v>
+        <v>8193</v>
       </c>
       <c r="M2" t="n">
-        <v>919</v>
+        <v>1453</v>
       </c>
     </row>
   </sheetData>
@@ -621,37 +621,37 @@
         <v>800</v>
       </c>
       <c r="C2" t="n">
-        <v>126</v>
+        <v>800</v>
       </c>
       <c r="D2" t="n">
-        <v>674</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.075</v>
+        <v>0.4825</v>
       </c>
       <c r="G2" t="n">
-        <v>0.485</v>
+        <v>0.4869558048729306</v>
       </c>
       <c r="H2" t="n">
-        <v>0.07369659202532675</v>
+        <v>0.489110372831303</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1230949313018894</v>
+        <v>0.4636437246963562</v>
       </c>
       <c r="J2" t="n">
-        <v>13</v>
+        <v>268</v>
       </c>
       <c r="K2" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="L2" t="n">
-        <v>13</v>
+        <v>295</v>
       </c>
       <c r="M2" t="n">
-        <v>47</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
@@ -664,37 +664,37 @@
         <v>800</v>
       </c>
       <c r="C3" t="n">
-        <v>143</v>
+        <v>800</v>
       </c>
       <c r="D3" t="n">
-        <v>657</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09375</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5297042325344212</v>
+        <v>0.4994397759103641</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09419691969196919</v>
+        <v>0.4996249624962497</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1549132269109503</v>
+        <v>0.4559534143024106</v>
       </c>
       <c r="J3" t="n">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="K3" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="L3" t="n">
-        <v>17</v>
+        <v>312</v>
       </c>
       <c r="M3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -707,37 +707,37 @@
         <v>1600</v>
       </c>
       <c r="C4" t="n">
-        <v>288</v>
+        <v>1600</v>
       </c>
       <c r="D4" t="n">
-        <v>1312</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08624999999999999</v>
+        <v>0.498125</v>
       </c>
       <c r="G4" t="n">
-        <v>0.4550391513008335</v>
+        <v>0.4905797101449275</v>
       </c>
       <c r="H4" t="n">
-        <v>0.08759004251366957</v>
+        <v>0.4923775601625495</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1422808823777617</v>
+        <v>0.469607931772293</v>
       </c>
       <c r="J4" t="n">
-        <v>30</v>
+        <v>584</v>
       </c>
       <c r="K4" t="n">
-        <v>106</v>
+        <v>237</v>
       </c>
       <c r="L4" t="n">
-        <v>44</v>
+        <v>566</v>
       </c>
       <c r="M4" t="n">
-        <v>108</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
@@ -750,37 +750,37 @@
         <v>1600</v>
       </c>
       <c r="C5" t="n">
-        <v>244</v>
+        <v>1600</v>
       </c>
       <c r="D5" t="n">
-        <v>1356</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.07875</v>
+        <v>0.50125</v>
       </c>
       <c r="G5" t="n">
-        <v>0.5161593764697977</v>
+        <v>0.4972720011699459</v>
       </c>
       <c r="H5" t="n">
-        <v>0.07878432751279346</v>
+        <v>0.4988632368451892</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1366996522631131</v>
+        <v>0.4144580434974025</v>
       </c>
       <c r="J5" t="n">
-        <v>59</v>
+        <v>709</v>
       </c>
       <c r="K5" t="n">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="L5" t="n">
-        <v>62</v>
+        <v>702</v>
       </c>
       <c r="M5" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -793,37 +793,37 @@
         <v>1600</v>
       </c>
       <c r="C6" t="n">
-        <v>268</v>
+        <v>1600</v>
       </c>
       <c r="D6" t="n">
-        <v>1332</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.083125</v>
+        <v>0.51</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4982129893337801</v>
+        <v>0.49961259777526</v>
       </c>
       <c r="H6" t="n">
-        <v>0.08313306512768956</v>
+        <v>0.4998444240484459</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1423821317189506</v>
+        <v>0.4166666666666666</v>
       </c>
       <c r="J6" t="n">
-        <v>68</v>
+        <v>728</v>
       </c>
       <c r="K6" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="L6" t="n">
-        <v>59</v>
+        <v>691</v>
       </c>
       <c r="M6" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -836,37 +836,37 @@
         <v>1600</v>
       </c>
       <c r="C7" t="n">
-        <v>260</v>
+        <v>1600</v>
       </c>
       <c r="D7" t="n">
-        <v>1340</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0775</v>
+        <v>0.46875</v>
       </c>
       <c r="G7" t="n">
-        <v>0.4798182304196739</v>
+        <v>0.5011845534233594</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0798240100565682</v>
+        <v>0.500345694531741</v>
       </c>
       <c r="I7" t="n">
-        <v>0.134112999107147</v>
+        <v>0.3770052643055166</v>
       </c>
       <c r="J7" t="n">
-        <v>82</v>
+        <v>682</v>
       </c>
       <c r="K7" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="L7" t="n">
-        <v>92</v>
+        <v>792</v>
       </c>
       <c r="M7" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -879,37 +879,37 @@
         <v>1600</v>
       </c>
       <c r="C8" t="n">
-        <v>271</v>
+        <v>1600</v>
       </c>
       <c r="D8" t="n">
-        <v>1329</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.091875</v>
+        <v>0.480625</v>
       </c>
       <c r="G8" t="n">
-        <v>0.5423565121412803</v>
+        <v>0.4901399491094147</v>
       </c>
       <c r="H8" t="n">
-        <v>0.09242550141697142</v>
+        <v>0.4993208552216688</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1574795409866045</v>
+        <v>0.3388097680712152</v>
       </c>
       <c r="J8" t="n">
-        <v>82</v>
+        <v>755</v>
       </c>
       <c r="K8" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="L8" t="n">
-        <v>69</v>
+        <v>817</v>
       </c>
       <c r="M8" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -922,37 +922,37 @@
         <v>1600</v>
       </c>
       <c r="C9" t="n">
-        <v>262</v>
+        <v>1600</v>
       </c>
       <c r="D9" t="n">
-        <v>1338</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.0775</v>
+        <v>0.509375</v>
       </c>
       <c r="G9" t="n">
-        <v>0.473257509477982</v>
+        <v>0.4982766864222841</v>
       </c>
       <c r="H9" t="n">
-        <v>0.07762745576342109</v>
+        <v>0.4992165950500066</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1333230229087631</v>
+        <v>0.4249692454690003</v>
       </c>
       <c r="J9" t="n">
-        <v>60</v>
+        <v>714</v>
       </c>
       <c r="K9" t="n">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="L9" t="n">
-        <v>67</v>
+        <v>677</v>
       </c>
       <c r="M9" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -965,37 +965,37 @@
         <v>1600</v>
       </c>
       <c r="C10" t="n">
-        <v>235</v>
+        <v>1600</v>
       </c>
       <c r="D10" t="n">
-        <v>1365</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.073125</v>
+        <v>0.505</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5031378877532724</v>
+        <v>0.5147916034906836</v>
       </c>
       <c r="H10" t="n">
-        <v>0.07297369934248356</v>
+        <v>0.5027438185954649</v>
       </c>
       <c r="I10" t="n">
-        <v>0.1247463414750467</v>
+        <v>0.3766614000326623</v>
       </c>
       <c r="J10" t="n">
-        <v>83</v>
+        <v>767</v>
       </c>
       <c r="K10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="L10" t="n">
-        <v>86</v>
+        <v>755</v>
       </c>
       <c r="M10" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -1008,37 +1008,37 @@
         <v>1600</v>
       </c>
       <c r="C11" t="n">
-        <v>246</v>
+        <v>1600</v>
       </c>
       <c r="D11" t="n">
-        <v>1354</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.07062499999999999</v>
+        <v>0.494375</v>
       </c>
       <c r="G11" t="n">
-        <v>0.476374269005848</v>
+        <v>0.4792992629963105</v>
       </c>
       <c r="H11" t="n">
-        <v>0.07096909304593534</v>
+        <v>0.4891881923432773</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1211321451201635</v>
+        <v>0.4223427162477268</v>
       </c>
       <c r="J11" t="n">
-        <v>39</v>
+        <v>678</v>
       </c>
       <c r="K11" t="n">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="L11" t="n">
-        <v>36</v>
+        <v>675</v>
       </c>
       <c r="M11" t="n">
-        <v>74</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -1051,37 +1051,37 @@
         <v>1600</v>
       </c>
       <c r="C12" t="n">
-        <v>255</v>
+        <v>1600</v>
       </c>
       <c r="D12" t="n">
-        <v>1345</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.0775</v>
+        <v>0.5024999999999999</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5003350308228357</v>
+        <v>0.5124639439707933</v>
       </c>
       <c r="H12" t="n">
-        <v>0.07729239078792728</v>
+        <v>0.5073203970893451</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1327024935190884</v>
+        <v>0.4481792862725931</v>
       </c>
       <c r="J12" t="n">
-        <v>50</v>
+        <v>653</v>
       </c>
       <c r="K12" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="L12" t="n">
-        <v>41</v>
+        <v>661</v>
       </c>
       <c r="M12" t="n">
-        <v>74</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
@@ -1094,37 +1094,37 @@
         <v>1600</v>
       </c>
       <c r="C13" t="n">
-        <v>260</v>
+        <v>1600</v>
       </c>
       <c r="D13" t="n">
-        <v>1340</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.08125</v>
+        <v>0.50625</v>
       </c>
       <c r="G13" t="n">
-        <v>0.4833613445378152</v>
+        <v>0.5017908092029382</v>
       </c>
       <c r="H13" t="n">
-        <v>0.08184036097031873</v>
+        <v>0.5010604362714529</v>
       </c>
       <c r="I13" t="n">
-        <v>0.1378762692793873</v>
+        <v>0.4469297600795301</v>
       </c>
       <c r="J13" t="n">
-        <v>37</v>
+        <v>667</v>
       </c>
       <c r="K13" t="n">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="L13" t="n">
-        <v>48</v>
+        <v>644</v>
       </c>
       <c r="M13" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14">
@@ -1137,37 +1137,37 @@
         <v>1600</v>
       </c>
       <c r="C14" t="n">
-        <v>304</v>
+        <v>1600</v>
       </c>
       <c r="D14" t="n">
-        <v>1296</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.100625</v>
+        <v>0.491875</v>
       </c>
       <c r="G14" t="n">
-        <v>0.543975043223333</v>
+        <v>0.5013298740775483</v>
       </c>
       <c r="H14" t="n">
-        <v>0.09825721153846154</v>
+        <v>0.5010516826923077</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1575010993732167</v>
+        <v>0.4685786071023684</v>
       </c>
       <c r="J14" t="n">
-        <v>30</v>
+        <v>561</v>
       </c>
       <c r="K14" t="n">
-        <v>120</v>
+        <v>207</v>
       </c>
       <c r="L14" t="n">
-        <v>23</v>
+        <v>606</v>
       </c>
       <c r="M14" t="n">
-        <v>131</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
@@ -1261,37 +1261,37 @@
         <v>192</v>
       </c>
       <c r="C2" t="n">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="D2" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="E2" t="n">
         <v>0</v>
       </c>
       <c r="F2" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G2" t="n">
-        <v>0.5181818181818182</v>
+        <v>0.5089909033213454</v>
       </c>
       <c r="H2" t="n">
-        <v>0.08786953201701755</v>
+        <v>0.5046361950474528</v>
       </c>
       <c r="I2" t="n">
-        <v>0.148125</v>
+        <v>0.4227994227994228</v>
       </c>
       <c r="J2" t="n">
-        <v>7</v>
+        <v>76</v>
       </c>
       <c r="K2" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="L2" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="M2" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
     </row>
     <row r="3">
@@ -1304,37 +1304,37 @@
         <v>192</v>
       </c>
       <c r="C3" t="n">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="D3" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="E3" t="n">
         <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.09375</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G3" t="n">
-        <v>0.4348739495798319</v>
+        <v>0.5066643882433356</v>
       </c>
       <c r="H3" t="n">
-        <v>0.09188660801564028</v>
+        <v>0.5042359074617139</v>
       </c>
       <c r="I3" t="n">
-        <v>0.1427819548872181</v>
+        <v>0.4496291261562102</v>
       </c>
       <c r="J3" t="n">
-        <v>3</v>
+        <v>75</v>
       </c>
       <c r="K3" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="L3" t="n">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="M3" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4">
@@ -1347,37 +1347,37 @@
         <v>192</v>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="D4" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="E4" t="n">
         <v>0</v>
       </c>
       <c r="F4" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.5729166666666666</v>
       </c>
       <c r="G4" t="n">
-        <v>0.5035087719298246</v>
+        <v>0.5397727272727273</v>
       </c>
       <c r="H4" t="n">
-        <v>0.09124168514412417</v>
+        <v>0.5124168514412417</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1531089108910891</v>
+        <v>0.4382760097045811</v>
       </c>
       <c r="J4" t="n">
+        <v>102</v>
+      </c>
+      <c r="K4" t="n">
         <v>8</v>
       </c>
-      <c r="K4" t="n">
-        <v>10</v>
-      </c>
       <c r="L4" t="n">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="M4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5">
@@ -1390,37 +1390,37 @@
         <v>192</v>
       </c>
       <c r="C5" t="n">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="D5" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E5" t="n">
         <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.109375</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6323529411764706</v>
+        <v>0.4348290598290598</v>
       </c>
       <c r="H5" t="n">
-        <v>0.1096581660336408</v>
+        <v>0.4602821486706457</v>
       </c>
       <c r="I5" t="n">
-        <v>0.1868678887484198</v>
+        <v>0.4033129167546692</v>
       </c>
       <c r="J5" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="K5" t="n">
-        <v>4</v>
+        <v>22</v>
       </c>
       <c r="L5" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="M5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="6">
@@ -1433,34 +1433,34 @@
         <v>192</v>
       </c>
       <c r="C6" t="n">
-        <v>37</v>
+        <v>192</v>
       </c>
       <c r="D6" t="n">
-        <v>155</v>
+        <v>0</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.515625</v>
       </c>
       <c r="G6" t="n">
-        <v>0.5733333333333333</v>
+        <v>0.4795296167247387</v>
       </c>
       <c r="H6" t="n">
-        <v>0.1062506817933893</v>
+        <v>0.4897458274244573</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1748283752860412</v>
+        <v>0.4284067991933161</v>
       </c>
       <c r="J6" t="n">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="K6" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="L6" t="n">
-        <v>4</v>
+        <v>77</v>
       </c>
       <c r="M6" t="n">
         <v>12</v>
@@ -1476,37 +1476,37 @@
         <v>192</v>
       </c>
       <c r="C7" t="n">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="D7" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
         <v>0</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1197916666666667</v>
+        <v>0.484375</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5431034482758621</v>
+        <v>0.4837105986883858</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1186495874945723</v>
+        <v>0.4916413373860182</v>
       </c>
       <c r="I7" t="n">
-        <v>0.1904620413014411</v>
+        <v>0.4176292165813904</v>
       </c>
       <c r="J7" t="n">
-        <v>6</v>
+        <v>79</v>
       </c>
       <c r="K7" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L7" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="M7" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
     </row>
     <row r="8">
@@ -1519,37 +1519,37 @@
         <v>192</v>
       </c>
       <c r="C8" t="n">
-        <v>38</v>
+        <v>192</v>
       </c>
       <c r="D8" t="n">
-        <v>154</v>
+        <v>0</v>
       </c>
       <c r="E8" t="n">
         <v>0</v>
       </c>
       <c r="F8" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G8" t="n">
-        <v>0.427536231884058</v>
+        <v>0.5692436974789916</v>
       </c>
       <c r="H8" t="n">
-        <v>0.08717391304347825</v>
+        <v>0.5223913043478261</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1442899475723729</v>
+        <v>0.4161144722942476</v>
       </c>
       <c r="J8" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="K8" t="n">
+        <v>6</v>
+      </c>
+      <c r="L8" t="n">
+        <v>89</v>
+      </c>
+      <c r="M8" t="n">
         <v>11</v>
-      </c>
-      <c r="L8" t="n">
-        <v>10</v>
-      </c>
-      <c r="M8" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="9">
@@ -1562,37 +1562,37 @@
         <v>192</v>
       </c>
       <c r="C9" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D9" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E9" t="n">
         <v>0</v>
       </c>
       <c r="F9" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G9" t="n">
-        <v>0.65</v>
+        <v>0.4259259259259259</v>
       </c>
       <c r="H9" t="n">
-        <v>0.1057692307692308</v>
+        <v>0.4606643356643357</v>
       </c>
       <c r="I9" t="n">
-        <v>0.1794380587484036</v>
+        <v>0.400535236396075</v>
       </c>
       <c r="J9" t="n">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="K9" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L9" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="M9" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="10">
@@ -1605,37 +1605,37 @@
         <v>192</v>
       </c>
       <c r="C10" t="n">
-        <v>41</v>
+        <v>192</v>
       </c>
       <c r="D10" t="n">
-        <v>151</v>
+        <v>0</v>
       </c>
       <c r="E10" t="n">
         <v>0</v>
       </c>
       <c r="F10" t="n">
-        <v>0.078125</v>
+        <v>0.546875</v>
       </c>
       <c r="G10" t="n">
-        <v>0.3809523809523809</v>
+        <v>0.5195286195286195</v>
       </c>
       <c r="H10" t="n">
-        <v>0.08062746818780167</v>
+        <v>0.5095436594997806</v>
       </c>
       <c r="I10" t="n">
-        <v>0.129646017699115</v>
+        <v>0.454527642621559</v>
       </c>
       <c r="J10" t="n">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="K10" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="L10" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="M10" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="11">
@@ -1648,37 +1648,37 @@
         <v>192</v>
       </c>
       <c r="C11" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D11" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
         <v>0</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0625</v>
+        <v>0.515625</v>
       </c>
       <c r="G11" t="n">
-        <v>0.3760683760683761</v>
+        <v>0.5401002506265664</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0625</v>
+        <v>0.515625</v>
       </c>
       <c r="I11" t="n">
-        <v>0.1068726863029132</v>
+        <v>0.428406799193316</v>
       </c>
       <c r="J11" t="n">
-        <v>4</v>
+        <v>87</v>
       </c>
       <c r="K11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L11" t="n">
-        <v>9</v>
+        <v>84</v>
       </c>
       <c r="M11" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="12">
@@ -1691,37 +1691,37 @@
         <v>192</v>
       </c>
       <c r="C12" t="n">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="D12" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="E12" t="n">
         <v>0</v>
       </c>
       <c r="F12" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4052631578947368</v>
+        <v>0.5558139534883721</v>
       </c>
       <c r="H12" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.5208333333333333</v>
       </c>
       <c r="I12" t="n">
-        <v>0.1158636897767333</v>
+        <v>0.4318064848172928</v>
       </c>
       <c r="J12" t="n">
-        <v>4</v>
+        <v>88</v>
       </c>
       <c r="K12" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="L12" t="n">
-        <v>15</v>
+        <v>84</v>
       </c>
       <c r="M12" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13">
@@ -1734,37 +1734,37 @@
         <v>192</v>
       </c>
       <c r="C13" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D13" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E13" t="n">
         <v>0</v>
       </c>
       <c r="F13" t="n">
-        <v>0.078125</v>
+        <v>0.46875</v>
       </c>
       <c r="G13" t="n">
-        <v>0.3787878787878788</v>
+        <v>0.433271547729379</v>
       </c>
       <c r="H13" t="n">
-        <v>0.078125</v>
+        <v>0.46875</v>
       </c>
       <c r="I13" t="n">
-        <v>0.129003914050643</v>
+        <v>0.3873107245651358</v>
       </c>
       <c r="J13" t="n">
-        <v>1</v>
+        <v>80</v>
       </c>
       <c r="K13" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L13" t="n">
+        <v>86</v>
+      </c>
+      <c r="M13" t="n">
         <v>10</v>
-      </c>
-      <c r="M13" t="n">
-        <v>14</v>
       </c>
     </row>
     <row r="14">
@@ -1777,37 +1777,37 @@
         <v>192</v>
       </c>
       <c r="C14" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D14" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E14" t="n">
         <v>0</v>
       </c>
       <c r="F14" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G14" t="n">
-        <v>0.4605263157894737</v>
+        <v>0.4732905982905983</v>
       </c>
       <c r="H14" t="n">
-        <v>0.07571570686415387</v>
+        <v>0.4834199182049298</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1280181494085237</v>
+        <v>0.4459489456159822</v>
       </c>
       <c r="J14" t="n">
-        <v>6</v>
+        <v>87</v>
       </c>
       <c r="K14" t="n">
-        <v>11</v>
+        <v>22</v>
       </c>
       <c r="L14" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="M14" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15">
@@ -1820,37 +1820,37 @@
         <v>192</v>
       </c>
       <c r="C15" t="n">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="D15" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="E15" t="n">
         <v>0</v>
       </c>
       <c r="F15" t="n">
-        <v>0.09375</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G15" t="n">
-        <v>0.5381944444444444</v>
+        <v>0.5384615384615384</v>
       </c>
       <c r="H15" t="n">
-        <v>0.09422492401215805</v>
+        <v>0.5180199739470256</v>
       </c>
       <c r="I15" t="n">
-        <v>0.1603448275862069</v>
+        <v>0.4401985111662531</v>
       </c>
       <c r="J15" t="n">
-        <v>11</v>
+        <v>83</v>
       </c>
       <c r="K15" t="n">
         <v>11</v>
       </c>
       <c r="L15" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="M15" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16">
@@ -1863,37 +1863,37 @@
         <v>192</v>
       </c>
       <c r="C16" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D16" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E16" t="n">
         <v>0</v>
       </c>
       <c r="F16" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.515625</v>
       </c>
       <c r="G16" t="n">
-        <v>0.53125</v>
+        <v>0.5787878787878787</v>
       </c>
       <c r="H16" t="n">
-        <v>0.08856209150326798</v>
+        <v>0.538235294117647</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1517428845538855</v>
+        <v>0.4571819425444597</v>
       </c>
       <c r="J16" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="K16" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L16" t="n">
-        <v>8</v>
+        <v>84</v>
       </c>
       <c r="M16" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
     </row>
     <row r="17">
@@ -1906,37 +1906,37 @@
         <v>192</v>
       </c>
       <c r="C17" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D17" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E17" t="n">
         <v>0</v>
       </c>
       <c r="F17" t="n">
-        <v>0.0625</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3925438596491228</v>
+        <v>0.5320742937412205</v>
       </c>
       <c r="H17" t="n">
-        <v>0.06239572906239572</v>
+        <v>0.5228561895228562</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1076095947063689</v>
+        <v>0.4579333709768492</v>
       </c>
       <c r="J17" t="n">
-        <v>5</v>
+        <v>65</v>
       </c>
       <c r="K17" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L17" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="M17" t="n">
-        <v>7</v>
+        <v>27</v>
       </c>
     </row>
     <row r="18">
@@ -1949,37 +1949,37 @@
         <v>192</v>
       </c>
       <c r="C18" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D18" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E18" t="n">
         <v>0</v>
       </c>
       <c r="F18" t="n">
-        <v>0.0625</v>
+        <v>0.53125</v>
       </c>
       <c r="G18" t="n">
-        <v>0.388663967611336</v>
+        <v>0.5099046221570066</v>
       </c>
       <c r="H18" t="n">
-        <v>0.06305418719211822</v>
+        <v>0.5073891625615763</v>
       </c>
       <c r="I18" t="n">
-        <v>0.1074512312120243</v>
+        <v>0.484179104477612</v>
       </c>
       <c r="J18" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="K18" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="L18" t="n">
-        <v>7</v>
+        <v>65</v>
       </c>
       <c r="M18" t="n">
-        <v>6</v>
+        <v>22</v>
       </c>
     </row>
     <row r="19">
@@ -1992,34 +1992,34 @@
         <v>192</v>
       </c>
       <c r="C19" t="n">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="D19" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="E19" t="n">
         <v>0</v>
       </c>
       <c r="F19" t="n">
-        <v>0.078125</v>
+        <v>0.484375</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4257246376811594</v>
+        <v>0.4553571428571429</v>
       </c>
       <c r="H19" t="n">
-        <v>0.07840477482365707</v>
+        <v>0.4804666304937601</v>
       </c>
       <c r="I19" t="n">
-        <v>0.1306173223448919</v>
+        <v>0.3972411606151894</v>
       </c>
       <c r="J19" t="n">
-        <v>5</v>
+        <v>83</v>
       </c>
       <c r="K19" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L19" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="M19" t="n">
         <v>10</v>
@@ -2035,37 +2035,37 @@
         <v>192</v>
       </c>
       <c r="C20" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D20" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E20" t="n">
         <v>0</v>
       </c>
       <c r="F20" t="n">
-        <v>0.09895833333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G20" t="n">
-        <v>0.5941176470588235</v>
+        <v>0.6006734006734007</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1000884271029071</v>
+        <v>0.5495744445672599</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1712018140589569</v>
+        <v>0.4535104364326376</v>
       </c>
       <c r="J20" t="n">
-        <v>9</v>
+        <v>76</v>
       </c>
       <c r="K20" t="n">
         <v>7</v>
       </c>
       <c r="L20" t="n">
-        <v>6</v>
+        <v>89</v>
       </c>
       <c r="M20" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="21">
@@ -2078,37 +2078,37 @@
         <v>192</v>
       </c>
       <c r="C21" t="n">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="D21" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="E21" t="n">
         <v>0</v>
       </c>
       <c r="F21" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.5364583333333334</v>
       </c>
       <c r="G21" t="n">
-        <v>0.5833333333333334</v>
+        <v>0.5645348837209303</v>
       </c>
       <c r="H21" t="n">
-        <v>0.104594330400782</v>
+        <v>0.5241120886282177</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1761372457692905</v>
+        <v>0.4419880481990661</v>
       </c>
       <c r="J21" t="n">
-        <v>9</v>
+        <v>91</v>
       </c>
       <c r="K21" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L21" t="n">
-        <v>5</v>
+        <v>81</v>
       </c>
       <c r="M21" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="22">
@@ -2121,37 +2121,37 @@
         <v>192</v>
       </c>
       <c r="C22" t="n">
+        <v>192</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" t="n">
+        <v>0</v>
+      </c>
+      <c r="F22" t="n">
+        <v>0.5052083333333334</v>
+      </c>
+      <c r="G22" t="n">
+        <v>0.5629839189994044</v>
+      </c>
+      <c r="H22" t="n">
+        <v>0.547047047047047</v>
+      </c>
+      <c r="I22" t="n">
+        <v>0.4882011279777771</v>
+      </c>
+      <c r="J22" t="n">
+        <v>66</v>
+      </c>
+      <c r="K22" t="n">
+        <v>15</v>
+      </c>
+      <c r="L22" t="n">
+        <v>80</v>
+      </c>
+      <c r="M22" t="n">
         <v>31</v>
-      </c>
-      <c r="D22" t="n">
-        <v>161</v>
-      </c>
-      <c r="E22" t="n">
-        <v>0</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0.078125</v>
-      </c>
-      <c r="G22" t="n">
-        <v>0.4807692307692308</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0.07757757757757758</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.1335972290945077</v>
-      </c>
-      <c r="J22" t="n">
-        <v>6</v>
-      </c>
-      <c r="K22" t="n">
-        <v>9</v>
-      </c>
-      <c r="L22" t="n">
-        <v>7</v>
-      </c>
-      <c r="M22" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="23">
@@ -2164,37 +2164,37 @@
         <v>192</v>
       </c>
       <c r="C23" t="n">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="D23" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E23" t="n">
         <v>0</v>
       </c>
       <c r="F23" t="n">
-        <v>0.078125</v>
+        <v>0.484375</v>
       </c>
       <c r="G23" t="n">
-        <v>0.4673913043478261</v>
+        <v>0.5852130325814536</v>
       </c>
       <c r="H23" t="n">
-        <v>0.07605820105820105</v>
+        <v>0.5337301587301587</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1295273672242975</v>
+        <v>0.4221614227086183</v>
       </c>
       <c r="J23" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="K23" t="n">
-        <v>13</v>
+        <v>6</v>
       </c>
       <c r="L23" t="n">
-        <v>5</v>
+        <v>93</v>
       </c>
       <c r="M23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="24">
@@ -2207,37 +2207,37 @@
         <v>192</v>
       </c>
       <c r="C24" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D24" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E24" t="n">
         <v>0</v>
       </c>
       <c r="F24" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.46875</v>
       </c>
       <c r="G24" t="n">
-        <v>0.3798076923076923</v>
+        <v>0.492553983618764</v>
       </c>
       <c r="H24" t="n">
-        <v>0.05725524475524475</v>
+        <v>0.4956293706293706</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0995049504950495</v>
+        <v>0.423117709437964</v>
       </c>
       <c r="J24" t="n">
-        <v>5</v>
+        <v>72</v>
       </c>
       <c r="K24" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L24" t="n">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="M24" t="n">
-        <v>6</v>
+        <v>18</v>
       </c>
     </row>
     <row r="25">
@@ -2250,37 +2250,37 @@
         <v>192</v>
       </c>
       <c r="C25" t="n">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="D25" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E25" t="n">
         <v>0</v>
       </c>
       <c r="F25" t="n">
-        <v>0.09375</v>
+        <v>0.515625</v>
       </c>
       <c r="G25" t="n">
-        <v>0.5714285714285714</v>
+        <v>0.5107142857142857</v>
       </c>
       <c r="H25" t="n">
-        <v>0.09416748126425546</v>
+        <v>0.5084718149234277</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1597913703176861</v>
+        <v>0.4847496753715193</v>
       </c>
       <c r="J25" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="K25" t="n">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="L25" t="n">
-        <v>4</v>
+        <v>67</v>
       </c>
       <c r="M25" t="n">
-        <v>10</v>
+        <v>26</v>
       </c>
     </row>
     <row r="26">
@@ -2293,37 +2293,37 @@
         <v>192</v>
       </c>
       <c r="C26" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D26" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E26" t="n">
         <v>0</v>
       </c>
       <c r="F26" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.4427083333333333</v>
       </c>
       <c r="G26" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.4540598290598291</v>
       </c>
       <c r="H26" t="n">
-        <v>0.08407224958949097</v>
+        <v>0.4717569786535304</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1453236232714181</v>
+        <v>0.4004027668330269</v>
       </c>
       <c r="J26" t="n">
-        <v>8</v>
+        <v>68</v>
       </c>
       <c r="K26" t="n">
-        <v>8</v>
+        <v>19</v>
       </c>
       <c r="L26" t="n">
-        <v>6</v>
+        <v>88</v>
       </c>
       <c r="M26" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
     </row>
     <row r="27">
@@ -2336,37 +2336,37 @@
         <v>192</v>
       </c>
       <c r="C27" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D27" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E27" t="n">
         <v>0</v>
       </c>
       <c r="F27" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G27" t="n">
-        <v>0.5227272727272727</v>
+        <v>0.5152439024390244</v>
       </c>
       <c r="H27" t="n">
-        <v>0.07257099336307257</v>
+        <v>0.5076161462300076</v>
       </c>
       <c r="I27" t="n">
-        <v>0.1271995977878331</v>
+        <v>0.4459489456159822</v>
       </c>
       <c r="J27" t="n">
-        <v>8</v>
+        <v>87</v>
       </c>
       <c r="K27" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="L27" t="n">
-        <v>8</v>
+        <v>77</v>
       </c>
       <c r="M27" t="n">
-        <v>6</v>
+        <v>14</v>
       </c>
     </row>
     <row r="28">
@@ -2379,37 +2379,37 @@
         <v>192</v>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D28" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E28" t="n">
         <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G28" t="n">
-        <v>0.4452380952380952</v>
+        <v>0.53125</v>
       </c>
       <c r="H28" t="n">
-        <v>0.06755290287574606</v>
+        <v>0.5095496473141616</v>
       </c>
       <c r="I28" t="n">
-        <v>0.117300131061599</v>
+        <v>0.4043692649315874</v>
       </c>
       <c r="J28" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="K28" t="n">
         <v>7</v>
       </c>
       <c r="L28" t="n">
+        <v>88</v>
+      </c>
+      <c r="M28" t="n">
         <v>9</v>
-      </c>
-      <c r="M28" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="29">
@@ -2422,37 +2422,37 @@
         <v>192</v>
       </c>
       <c r="C29" t="n">
-        <v>45</v>
+        <v>192</v>
       </c>
       <c r="D29" t="n">
-        <v>147</v>
+        <v>0</v>
       </c>
       <c r="E29" t="n">
         <v>0</v>
       </c>
       <c r="F29" t="n">
-        <v>0.1302083333333333</v>
+        <v>0.484375</v>
       </c>
       <c r="G29" t="n">
-        <v>0.55</v>
+        <v>0.5033920206751736</v>
       </c>
       <c r="H29" t="n">
-        <v>0.1277777777777778</v>
+        <v>0.5022875816993464</v>
       </c>
       <c r="I29" t="n">
-        <v>0.204978354978355</v>
+        <v>0.4484519629747846</v>
       </c>
       <c r="J29" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="K29" t="n">
-        <v>13</v>
+        <v>19</v>
       </c>
       <c r="L29" t="n">
-        <v>7</v>
+        <v>80</v>
       </c>
       <c r="M29" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="30">
@@ -2465,37 +2465,37 @@
         <v>192</v>
       </c>
       <c r="C30" t="n">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="D30" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E30" t="n">
         <v>0</v>
       </c>
       <c r="F30" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G30" t="n">
-        <v>0.4944444444444445</v>
+        <v>0.4419955920657183</v>
       </c>
       <c r="H30" t="n">
-        <v>0.083088954056696</v>
+        <v>0.4685565330726621</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1420104314841157</v>
+        <v>0.4044665012406948</v>
       </c>
       <c r="J30" t="n">
-        <v>9</v>
+        <v>80</v>
       </c>
       <c r="K30" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="L30" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="M30" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="31">
@@ -2508,37 +2508,37 @@
         <v>192</v>
       </c>
       <c r="C31" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D31" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E31" t="n">
         <v>0</v>
       </c>
       <c r="F31" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.46875</v>
       </c>
       <c r="G31" t="n">
-        <v>0.4285714285714286</v>
+        <v>0.46875</v>
       </c>
       <c r="H31" t="n">
-        <v>0.07217391304347825</v>
+        <v>0.4826086956521739</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1234409977614327</v>
+        <v>0.4112554112554113</v>
       </c>
       <c r="J31" t="n">
-        <v>5</v>
+        <v>75</v>
       </c>
       <c r="K31" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L31" t="n">
-        <v>9</v>
+        <v>85</v>
       </c>
       <c r="M31" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="32">
@@ -2551,37 +2551,37 @@
         <v>192</v>
       </c>
       <c r="C32" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D32" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E32" t="n">
         <v>0</v>
       </c>
       <c r="F32" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G32" t="n">
-        <v>0.4452380952380952</v>
+        <v>0.5135329341317365</v>
       </c>
       <c r="H32" t="n">
-        <v>0.06692483909676011</v>
+        <v>0.506163412239555</v>
       </c>
       <c r="I32" t="n">
-        <v>0.1163402994898799</v>
+        <v>0.4140625</v>
       </c>
       <c r="J32" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="K32" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="L32" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="M32" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="33">
@@ -2594,37 +2594,37 @@
         <v>192</v>
       </c>
       <c r="C33" t="n">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="D33" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="E33" t="n">
         <v>0</v>
       </c>
       <c r="F33" t="n">
-        <v>0.09895833333333333</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G33" t="n">
-        <v>0.554945054945055</v>
+        <v>0.5714285714285714</v>
       </c>
       <c r="H33" t="n">
-        <v>0.09845853234910985</v>
+        <v>0.5193226226660878</v>
       </c>
       <c r="I33" t="n">
-        <v>0.1662608968821173</v>
+        <v>0.407563025210084</v>
       </c>
       <c r="J33" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="K33" t="n">
+        <v>5</v>
+      </c>
+      <c r="L33" t="n">
+        <v>89</v>
+      </c>
+      <c r="M33" t="n">
         <v>9</v>
-      </c>
-      <c r="L33" t="n">
-        <v>6</v>
-      </c>
-      <c r="M33" t="n">
-        <v>12</v>
       </c>
     </row>
     <row r="34">
@@ -2637,37 +2637,37 @@
         <v>192</v>
       </c>
       <c r="C34" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D34" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E34" t="n">
         <v>0</v>
       </c>
       <c r="F34" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G34" t="n">
-        <v>0.5147058823529411</v>
+        <v>0.5351384240949194</v>
       </c>
       <c r="H34" t="n">
-        <v>0.083088954056696</v>
+        <v>0.5125448028673835</v>
       </c>
       <c r="I34" t="n">
-        <v>0.1430067676442153</v>
+        <v>0.412769211163502</v>
       </c>
       <c r="J34" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="K34" t="n">
         <v>8</v>
       </c>
       <c r="L34" t="n">
-        <v>7</v>
+        <v>88</v>
       </c>
       <c r="M34" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="35">
@@ -2680,37 +2680,37 @@
         <v>192</v>
       </c>
       <c r="C35" t="n">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="D35" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G35" t="n">
-        <v>0.5227272727272727</v>
+        <v>0.510194624652456</v>
       </c>
       <c r="H35" t="n">
-        <v>0.08760869565217391</v>
+        <v>0.5047826086956522</v>
       </c>
       <c r="I35" t="n">
-        <v>0.1484163616106955</v>
+        <v>0.421188630490956</v>
       </c>
       <c r="J35" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="K35" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="L35" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="M35" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="36">
@@ -2723,37 +2723,37 @@
         <v>192</v>
       </c>
       <c r="C36" t="n">
-        <v>40</v>
+        <v>192</v>
       </c>
       <c r="D36" t="n">
-        <v>152</v>
+        <v>0</v>
       </c>
       <c r="E36" t="n">
         <v>0</v>
       </c>
       <c r="F36" t="n">
-        <v>0.1197916666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G36" t="n">
-        <v>0.59375</v>
+        <v>0.5617283950617283</v>
       </c>
       <c r="H36" t="n">
-        <v>0.1130952380952381</v>
+        <v>0.533068783068783</v>
       </c>
       <c r="I36" t="n">
-        <v>0.1829192546583851</v>
+        <v>0.4457405443619653</v>
       </c>
       <c r="J36" t="n">
-        <v>5</v>
+        <v>74</v>
       </c>
       <c r="K36" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L36" t="n">
-        <v>3</v>
+        <v>88</v>
       </c>
       <c r="M36" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
     </row>
     <row r="37">
@@ -2766,37 +2766,37 @@
         <v>192</v>
       </c>
       <c r="C37" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D37" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
       </c>
       <c r="F37" t="n">
-        <v>0.078125</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G37" t="n">
-        <v>0.5773809523809523</v>
+        <v>0.4614977787180029</v>
       </c>
       <c r="H37" t="n">
-        <v>0.07847826086956522</v>
+        <v>0.4802173913043478</v>
       </c>
       <c r="I37" t="n">
-        <v>0.1379716981132076</v>
+        <v>0.4147629073311755</v>
       </c>
       <c r="J37" t="n">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="K37" t="n">
-        <v>6</v>
+        <v>17</v>
       </c>
       <c r="L37" t="n">
-        <v>5</v>
+        <v>80</v>
       </c>
       <c r="M37" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
     </row>
     <row r="38">
@@ -2809,37 +2809,37 @@
         <v>192</v>
       </c>
       <c r="C38" t="n">
-        <v>25</v>
+        <v>192</v>
       </c>
       <c r="D38" t="n">
-        <v>167</v>
+        <v>0</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G38" t="n">
-        <v>0.4333333333333333</v>
+        <v>0.475</v>
       </c>
       <c r="H38" t="n">
-        <v>0.0576422058184976</v>
+        <v>0.4834997828918801</v>
       </c>
       <c r="I38" t="n">
-        <v>0.1012572205232756</v>
+        <v>0.4383283582089552</v>
       </c>
       <c r="J38" t="n">
-        <v>4</v>
+        <v>76</v>
       </c>
       <c r="K38" t="n">
-        <v>8</v>
+        <v>22</v>
       </c>
       <c r="L38" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="M38" t="n">
-        <v>7</v>
+        <v>18</v>
       </c>
     </row>
     <row r="39">
@@ -2852,37 +2852,37 @@
         <v>192</v>
       </c>
       <c r="C39" t="n">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="D39" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E39" t="n">
         <v>0</v>
       </c>
       <c r="F39" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5037593984962406</v>
+        <v>0.5052264808362369</v>
       </c>
       <c r="H39" t="n">
-        <v>0.08664021164021163</v>
+        <v>0.5026455026455026</v>
       </c>
       <c r="I39" t="n">
-        <v>0.1478386630242648</v>
+        <v>0.4079696394686907</v>
       </c>
       <c r="J39" t="n">
-        <v>6</v>
+        <v>72</v>
       </c>
       <c r="K39" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="L39" t="n">
-        <v>8</v>
+        <v>92</v>
       </c>
       <c r="M39" t="n">
-        <v>11</v>
+        <v>16</v>
       </c>
     </row>
     <row r="40">
@@ -2895,37 +2895,37 @@
         <v>192</v>
       </c>
       <c r="C40" t="n">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="D40" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="E40" t="n">
         <v>0</v>
       </c>
       <c r="F40" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.484375</v>
       </c>
       <c r="G40" t="n">
-        <v>0.4039855072463768</v>
+        <v>0.4605488850771869</v>
       </c>
       <c r="H40" t="n">
-        <v>0.07338254450716457</v>
+        <v>0.4775293095961789</v>
       </c>
       <c r="I40" t="n">
-        <v>0.1223776223776224</v>
+        <v>0.4176292165813904</v>
       </c>
       <c r="J40" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="K40" t="n">
+        <v>19</v>
+      </c>
+      <c r="L40" t="n">
+        <v>80</v>
+      </c>
+      <c r="M40" t="n">
         <v>14</v>
-      </c>
-      <c r="L40" t="n">
-        <v>7</v>
-      </c>
-      <c r="M40" t="n">
-        <v>9</v>
       </c>
     </row>
     <row r="41">
@@ -2938,34 +2938,34 @@
         <v>192</v>
       </c>
       <c r="C41" t="n">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="D41" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E41" t="n">
         <v>0</v>
       </c>
       <c r="F41" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G41" t="n">
-        <v>0.4545454545454545</v>
+        <v>0.4087542087542088</v>
       </c>
       <c r="H41" t="n">
-        <v>0.07454844006568144</v>
+        <v>0.4555008210180624</v>
       </c>
       <c r="I41" t="n">
-        <v>0.1251186333438785</v>
+        <v>0.3886939571150098</v>
       </c>
       <c r="J41" t="n">
-        <v>6</v>
+        <v>86</v>
       </c>
       <c r="K41" t="n">
-        <v>14</v>
+        <v>19</v>
       </c>
       <c r="L41" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="M41" t="n">
         <v>8</v>
@@ -2981,34 +2981,34 @@
         <v>192</v>
       </c>
       <c r="C42" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D42" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E42" t="n">
         <v>0</v>
       </c>
       <c r="F42" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4322916666666667</v>
       </c>
       <c r="G42" t="n">
-        <v>0.4142857142857143</v>
+        <v>0.4077380952380952</v>
       </c>
       <c r="H42" t="n">
-        <v>0.06616123050070907</v>
+        <v>0.4594196574670012</v>
       </c>
       <c r="I42" t="n">
-        <v>0.1129846855653307</v>
+        <v>0.358803884922945</v>
       </c>
       <c r="J42" t="n">
-        <v>4</v>
+        <v>74</v>
       </c>
       <c r="K42" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="L42" t="n">
-        <v>6</v>
+        <v>94</v>
       </c>
       <c r="M42" t="n">
         <v>9</v>
@@ -3024,37 +3024,37 @@
         <v>192</v>
       </c>
       <c r="C43" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D43" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E43" t="n">
         <v>0</v>
       </c>
       <c r="F43" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G43" t="n">
-        <v>0.40625</v>
+        <v>0.4478639930252833</v>
       </c>
       <c r="H43" t="n">
-        <v>0.06784628745115068</v>
+        <v>0.4675423360833695</v>
       </c>
       <c r="I43" t="n">
-        <v>0.116267942583732</v>
+        <v>0.4148990737108892</v>
       </c>
       <c r="J43" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="K43" t="n">
-        <v>9</v>
+        <v>22</v>
       </c>
       <c r="L43" t="n">
-        <v>10</v>
+        <v>79</v>
       </c>
       <c r="M43" t="n">
-        <v>7</v>
+        <v>15</v>
       </c>
     </row>
     <row r="44">
@@ -3067,37 +3067,37 @@
         <v>192</v>
       </c>
       <c r="C44" t="n">
-        <v>36</v>
+        <v>192</v>
       </c>
       <c r="D44" t="n">
-        <v>156</v>
+        <v>0</v>
       </c>
       <c r="E44" t="n">
         <v>0</v>
       </c>
       <c r="F44" t="n">
-        <v>0.09375</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G44" t="n">
-        <v>0.5812807881773399</v>
+        <v>0.4516833484986351</v>
       </c>
       <c r="H44" t="n">
-        <v>0.1027694361027694</v>
+        <v>0.4704704704704705</v>
       </c>
       <c r="I44" t="n">
-        <v>0.1605546995377504</v>
+        <v>0.4318064848172928</v>
       </c>
       <c r="J44" t="n">
-        <v>5</v>
+        <v>88</v>
       </c>
       <c r="K44" t="n">
-        <v>16</v>
+        <v>23</v>
       </c>
       <c r="L44" t="n">
-        <v>2</v>
+        <v>69</v>
       </c>
       <c r="M44" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
     </row>
     <row r="45">
@@ -3110,37 +3110,37 @@
         <v>192</v>
       </c>
       <c r="C45" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D45" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E45" t="n">
         <v>0</v>
       </c>
       <c r="F45" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.4947916666666667</v>
       </c>
       <c r="G45" t="n">
-        <v>0.5520361990950227</v>
+        <v>0.4969879518072289</v>
       </c>
       <c r="H45" t="n">
-        <v>0.08323385784047749</v>
+        <v>0.4985892566467716</v>
       </c>
       <c r="I45" t="n">
-        <v>0.1443181818181818</v>
+        <v>0.4198673021212971</v>
       </c>
       <c r="J45" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="K45" t="n">
-        <v>4</v>
+        <v>13</v>
       </c>
       <c r="L45" t="n">
-        <v>10</v>
+        <v>84</v>
       </c>
       <c r="M45" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="46">
@@ -3153,37 +3153,37 @@
         <v>192</v>
       </c>
       <c r="C46" t="n">
-        <v>24</v>
+        <v>192</v>
       </c>
       <c r="D46" t="n">
-        <v>168</v>
+        <v>0</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="n">
-        <v>0.078125</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G46" t="n">
-        <v>0.6188811188811189</v>
+        <v>0.4702380952380952</v>
       </c>
       <c r="H46" t="n">
-        <v>0.07745098039215687</v>
+        <v>0.4869281045751634</v>
       </c>
       <c r="I46" t="n">
-        <v>0.1376668101592768</v>
+        <v>0.41364522417154</v>
       </c>
       <c r="J46" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="K46" t="n">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="L46" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="M46" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="47">
@@ -3196,37 +3196,37 @@
         <v>192</v>
       </c>
       <c r="C47" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D47" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
       </c>
       <c r="F47" t="n">
-        <v>0.09375</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G47" t="n">
-        <v>0.6</v>
+        <v>0.490625</v>
       </c>
       <c r="H47" t="n">
-        <v>0.09416748126425546</v>
+        <v>0.4947865754317367</v>
       </c>
       <c r="I47" t="n">
-        <v>0.1627680311890838</v>
+        <v>0.4366023166023166</v>
       </c>
       <c r="J47" t="n">
-        <v>8</v>
+        <v>82</v>
       </c>
       <c r="K47" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
       <c r="L47" t="n">
-        <v>7</v>
+        <v>78</v>
       </c>
       <c r="M47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="48">
@@ -3239,37 +3239,37 @@
         <v>192</v>
       </c>
       <c r="C48" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D48" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
       </c>
       <c r="F48" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5941176470588235</v>
+        <v>0.5232323232323233</v>
       </c>
       <c r="H48" t="n">
-        <v>0.08276311502117953</v>
+        <v>0.5112414467253177</v>
       </c>
       <c r="I48" t="n">
-        <v>0.1444593237361901</v>
+        <v>0.4330011074197121</v>
       </c>
       <c r="J48" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="K48" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
       <c r="L48" t="n">
-        <v>4</v>
+        <v>84</v>
       </c>
       <c r="M48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="49">
@@ -3282,37 +3282,37 @@
         <v>192</v>
       </c>
       <c r="C49" t="n">
-        <v>43</v>
+        <v>192</v>
       </c>
       <c r="D49" t="n">
-        <v>149</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
       </c>
       <c r="F49" t="n">
-        <v>0.1302083333333333</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G49" t="n">
-        <v>0.5648148148148149</v>
+        <v>0.5019736842105263</v>
       </c>
       <c r="H49" t="n">
-        <v>0.1269293924466338</v>
+        <v>0.5013136288998358</v>
       </c>
       <c r="I49" t="n">
-        <v>0.2064577817005002</v>
+        <v>0.4404270668013274</v>
       </c>
       <c r="J49" t="n">
-        <v>8</v>
+        <v>69</v>
       </c>
       <c r="K49" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L49" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="M49" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
     </row>
     <row r="50">
@@ -3325,37 +3325,37 @@
         <v>192</v>
       </c>
       <c r="C50" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D50" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
       </c>
       <c r="F50" t="n">
-        <v>0.0625</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="G50" t="n">
-        <v>0.3643724696356275</v>
+        <v>0.456813104988831</v>
       </c>
       <c r="H50" t="n">
-        <v>0.06118881118881119</v>
+        <v>0.4746503496503496</v>
       </c>
       <c r="I50" t="n">
-        <v>0.1046446108025437</v>
+        <v>0.4004948745139625</v>
       </c>
       <c r="J50" t="n">
-        <v>4</v>
+        <v>70</v>
       </c>
       <c r="K50" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="L50" t="n">
-        <v>9</v>
+        <v>88</v>
       </c>
       <c r="M50" t="n">
-        <v>8</v>
+        <v>16</v>
       </c>
     </row>
     <row r="51">
@@ -3368,37 +3368,37 @@
         <v>192</v>
       </c>
       <c r="C51" t="n">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="D51" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
       </c>
       <c r="F51" t="n">
-        <v>0.09895833333333333</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G51" t="n">
-        <v>0.5555555555555556</v>
+        <v>0.53125</v>
       </c>
       <c r="H51" t="n">
-        <v>0.09833916083916083</v>
+        <v>0.5174825174825175</v>
       </c>
       <c r="I51" t="n">
-        <v>0.1670870113493064</v>
+        <v>0.4421252371916509</v>
       </c>
       <c r="J51" t="n">
-        <v>8</v>
+        <v>75</v>
       </c>
       <c r="K51" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L51" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="M51" t="n">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="52">
@@ -3411,37 +3411,37 @@
         <v>192</v>
       </c>
       <c r="C52" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D52" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
       </c>
       <c r="F52" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.515625</v>
       </c>
       <c r="G52" t="n">
-        <v>0.5994318181818181</v>
+        <v>0.5576923076923077</v>
       </c>
       <c r="H52" t="n">
-        <v>0.08374063212772889</v>
+        <v>0.5270446399478658</v>
       </c>
       <c r="I52" t="n">
-        <v>0.1462051709758131</v>
+        <v>0.4484633204633204</v>
       </c>
       <c r="J52" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="K52" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="L52" t="n">
-        <v>7</v>
+        <v>83</v>
       </c>
       <c r="M52" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="53">
@@ -3454,37 +3454,37 @@
         <v>192</v>
       </c>
       <c r="C53" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D53" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
       </c>
       <c r="F53" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G53" t="n">
-        <v>0.5357142857142857</v>
+        <v>0.5104427736006684</v>
       </c>
       <c r="H53" t="n">
-        <v>0.08334237655995659</v>
+        <v>0.5040694519804666</v>
       </c>
       <c r="I53" t="n">
-        <v>0.1441441441441441</v>
+        <v>0.412769211163502</v>
       </c>
       <c r="J53" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="K53" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="L53" t="n">
-        <v>8</v>
+        <v>86</v>
       </c>
       <c r="M53" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="54">
@@ -3497,37 +3497,37 @@
         <v>192</v>
       </c>
       <c r="C54" t="n">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="D54" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E54" t="n">
         <v>0</v>
       </c>
       <c r="F54" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G54" t="n">
-        <v>0.4868421052631579</v>
+        <v>0.5198653198653198</v>
       </c>
       <c r="H54" t="n">
-        <v>0.08374063212772889</v>
+        <v>0.5096122515477355</v>
       </c>
       <c r="I54" t="n">
-        <v>0.1423040455120101</v>
+        <v>0.4424242424242424</v>
       </c>
       <c r="J54" t="n">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="K54" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L54" t="n">
-        <v>7</v>
+        <v>79</v>
       </c>
       <c r="M54" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="55">
@@ -3540,37 +3540,37 @@
         <v>192</v>
       </c>
       <c r="C55" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D55" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E55" t="n">
         <v>0</v>
       </c>
       <c r="F55" t="n">
-        <v>0.078125</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G55" t="n">
-        <v>0.5120192307692308</v>
+        <v>0.5336898395721925</v>
       </c>
       <c r="H55" t="n">
-        <v>0.07745098039215687</v>
+        <v>0.5137254901960784</v>
       </c>
       <c r="I55" t="n">
-        <v>0.134523613625144</v>
+        <v>0.4163771712158809</v>
       </c>
       <c r="J55" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="K55" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="L55" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="M55" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
     </row>
     <row r="56">
@@ -3583,37 +3583,37 @@
         <v>192</v>
       </c>
       <c r="C56" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D56" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E56" t="n">
         <v>0</v>
       </c>
       <c r="F56" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G56" t="n">
-        <v>0.420940170940171</v>
+        <v>0.3788121990369181</v>
       </c>
       <c r="H56" t="n">
-        <v>0.07207989578810248</v>
+        <v>0.467216673903604</v>
       </c>
       <c r="I56" t="n">
-        <v>0.1228649693844666</v>
+        <v>0.3445378151260504</v>
       </c>
       <c r="J56" t="n">
-        <v>3</v>
+        <v>84</v>
       </c>
       <c r="K56" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L56" t="n">
-        <v>10</v>
+        <v>94</v>
       </c>
       <c r="M56" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
     </row>
     <row r="57">
@@ -3626,37 +3626,37 @@
         <v>192</v>
       </c>
       <c r="C57" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D57" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E57" t="n">
         <v>0</v>
       </c>
       <c r="F57" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G57" t="n">
-        <v>0.5432692307692308</v>
+        <v>0.5273958112968056</v>
       </c>
       <c r="H57" t="n">
-        <v>0.08355941399891481</v>
+        <v>0.5140531741725448</v>
       </c>
       <c r="I57" t="n">
-        <v>0.1446355446355446</v>
+        <v>0.4448135843484681</v>
       </c>
       <c r="J57" t="n">
-        <v>10</v>
+        <v>82</v>
       </c>
       <c r="K57" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L57" t="n">
-        <v>6</v>
+        <v>81</v>
       </c>
       <c r="M57" t="n">
-        <v>6</v>
+        <v>16</v>
       </c>
     </row>
     <row r="58">
@@ -3669,37 +3669,37 @@
         <v>192</v>
       </c>
       <c r="C58" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D58" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
       </c>
       <c r="F58" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.484375</v>
       </c>
       <c r="G58" t="n">
-        <v>0.6527777777777778</v>
+        <v>0.5198863636363636</v>
       </c>
       <c r="H58" t="n">
-        <v>0.1028179741051028</v>
+        <v>0.5060929169840062</v>
       </c>
       <c r="I58" t="n">
-        <v>0.1772048625275353</v>
+        <v>0.3915298184961107</v>
       </c>
       <c r="J58" t="n">
+        <v>84</v>
+      </c>
+      <c r="K58" t="n">
         <v>7</v>
       </c>
-      <c r="K58" t="n">
-        <v>5</v>
-      </c>
       <c r="L58" t="n">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="M58" t="n">
-        <v>13</v>
+        <v>9</v>
       </c>
     </row>
     <row r="59">
@@ -3712,37 +3712,37 @@
         <v>192</v>
       </c>
       <c r="C59" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D59" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E59" t="n">
         <v>0</v>
       </c>
       <c r="F59" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.4375</v>
       </c>
       <c r="G59" t="n">
-        <v>0.5852272727272727</v>
+        <v>0.4314179796107507</v>
       </c>
       <c r="H59" t="n">
-        <v>0.08566433566433566</v>
+        <v>0.4676573426573427</v>
       </c>
       <c r="I59" t="n">
-        <v>0.1483277591973244</v>
+        <v>0.3720169594185342</v>
       </c>
       <c r="J59" t="n">
-        <v>10</v>
+        <v>73</v>
       </c>
       <c r="K59" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
       <c r="L59" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="M59" t="n">
-        <v>6</v>
+        <v>11</v>
       </c>
     </row>
     <row r="60">
@@ -3755,34 +3755,34 @@
         <v>192</v>
       </c>
       <c r="C60" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D60" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E60" t="n">
         <v>0</v>
       </c>
       <c r="F60" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5885416666666666</v>
       </c>
       <c r="G60" t="n">
-        <v>0.5166666666666666</v>
+        <v>0.5806581059390048</v>
       </c>
       <c r="H60" t="n">
-        <v>0.08541875208541874</v>
+        <v>0.5223556890223557</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1459662902961872</v>
+        <v>0.447532325623748</v>
       </c>
       <c r="J60" t="n">
-        <v>8</v>
+        <v>105</v>
       </c>
       <c r="K60" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L60" t="n">
-        <v>7</v>
+        <v>73</v>
       </c>
       <c r="M60" t="n">
         <v>8</v>
@@ -3798,37 +3798,37 @@
         <v>192</v>
       </c>
       <c r="C61" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D61" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E61" t="n">
         <v>0</v>
       </c>
       <c r="F61" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G61" t="n">
-        <v>0.648989898989899</v>
+        <v>0.5061728395061729</v>
       </c>
       <c r="H61" t="n">
-        <v>0.08868866695614416</v>
+        <v>0.5032566217976553</v>
       </c>
       <c r="I61" t="n">
-        <v>0.1523525620367386</v>
+        <v>0.4401985111662531</v>
       </c>
       <c r="J61" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="K61" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="L61" t="n">
-        <v>1</v>
+        <v>79</v>
       </c>
       <c r="M61" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="62">
@@ -3841,37 +3841,37 @@
         <v>192</v>
       </c>
       <c r="C62" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D62" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E62" t="n">
         <v>0</v>
       </c>
       <c r="F62" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.578125</v>
       </c>
       <c r="G62" t="n">
-        <v>0.4914772727272727</v>
+        <v>0.5841750841750841</v>
       </c>
       <c r="H62" t="n">
-        <v>0.06899956121105749</v>
+        <v>0.5411364633611233</v>
       </c>
       <c r="I62" t="n">
-        <v>0.1199095022624434</v>
+        <v>0.4921464258890377</v>
       </c>
       <c r="J62" t="n">
-        <v>6</v>
+        <v>95</v>
       </c>
       <c r="K62" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="L62" t="n">
-        <v>5</v>
+        <v>70</v>
       </c>
       <c r="M62" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
     </row>
     <row r="63">
@@ -3884,37 +3884,37 @@
         <v>192</v>
       </c>
       <c r="C63" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D63" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E63" t="n">
         <v>0</v>
       </c>
       <c r="F63" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.484375</v>
       </c>
       <c r="G63" t="n">
-        <v>0.3035714285714286</v>
+        <v>0.5335329341317365</v>
       </c>
       <c r="H63" t="n">
-        <v>0.04108391608391608</v>
+        <v>0.5152972027972028</v>
       </c>
       <c r="I63" t="n">
-        <v>0.07237288135593221</v>
+        <v>0.4221614227086183</v>
       </c>
       <c r="J63" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="K63" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="L63" t="n">
-        <v>9</v>
+        <v>89</v>
       </c>
       <c r="M63" t="n">
-        <v>5</v>
+        <v>15</v>
       </c>
     </row>
     <row r="64">
@@ -3927,37 +3927,37 @@
         <v>192</v>
       </c>
       <c r="C64" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D64" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E64" t="n">
         <v>0</v>
       </c>
       <c r="F64" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="G64" t="n">
-        <v>0.5023923444976076</v>
+        <v>0.5257192676547515</v>
       </c>
       <c r="H64" t="n">
-        <v>0.07311500380807312</v>
+        <v>0.516048308127516</v>
       </c>
       <c r="I64" t="n">
-        <v>0.1269607843137255</v>
+        <v>0.457051961823966</v>
       </c>
       <c r="J64" t="n">
-        <v>7</v>
+        <v>75</v>
       </c>
       <c r="K64" t="n">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="L64" t="n">
-        <v>4</v>
+        <v>80</v>
       </c>
       <c r="M64" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
     </row>
     <row r="65">
@@ -3970,37 +3970,37 @@
         <v>192</v>
       </c>
       <c r="C65" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D65" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E65" t="n">
         <v>0</v>
       </c>
       <c r="F65" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.484375</v>
       </c>
       <c r="G65" t="n">
-        <v>0.4058823529411765</v>
+        <v>0.4732142857142857</v>
       </c>
       <c r="H65" t="n">
-        <v>0.06766142159522517</v>
+        <v>0.4882799782962561</v>
       </c>
       <c r="I65" t="n">
-        <v>0.1159489633173844</v>
+        <v>0.4026961631524369</v>
       </c>
       <c r="J65" t="n">
-        <v>6</v>
+        <v>82</v>
       </c>
       <c r="K65" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="L65" t="n">
-        <v>9</v>
+        <v>86</v>
       </c>
       <c r="M65" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
     </row>
     <row r="66">
@@ -4013,37 +4013,37 @@
         <v>192</v>
       </c>
       <c r="C66" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D66" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E66" t="n">
         <v>0</v>
       </c>
       <c r="F66" t="n">
-        <v>0.0625</v>
+        <v>0.453125</v>
       </c>
       <c r="G66" t="n">
-        <v>0.3973214285714286</v>
+        <v>0.4993827160493827</v>
       </c>
       <c r="H66" t="n">
-        <v>0.06510445451530894</v>
+        <v>0.4996683983640986</v>
       </c>
       <c r="I66" t="n">
-        <v>0.1113574772111358</v>
+        <v>0.408016443987667</v>
       </c>
       <c r="J66" t="n">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="K66" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="L66" t="n">
-        <v>9</v>
+        <v>92</v>
       </c>
       <c r="M66" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="67">
@@ -4056,37 +4056,37 @@
         <v>192</v>
       </c>
       <c r="C67" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D67" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E67" t="n">
         <v>0</v>
       </c>
       <c r="F67" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.4791666666666667</v>
       </c>
       <c r="G67" t="n">
-        <v>0.5547619047619048</v>
+        <v>0.488235294117647</v>
       </c>
       <c r="H67" t="n">
-        <v>0.08304347826086957</v>
+        <v>0.4952173913043478</v>
       </c>
       <c r="I67" t="n">
-        <v>0.1443679291687162</v>
+        <v>0.399324239769741</v>
       </c>
       <c r="J67" t="n">
-        <v>7</v>
+        <v>81</v>
       </c>
       <c r="K67" t="n">
-        <v>5</v>
+        <v>11</v>
       </c>
       <c r="L67" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="M67" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
     </row>
     <row r="68">
@@ -4099,37 +4099,37 @@
         <v>192</v>
       </c>
       <c r="C68" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D68" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E68" t="n">
         <v>0</v>
       </c>
       <c r="F68" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G68" t="n">
-        <v>0.3687782805429864</v>
+        <v>0.4545454545454546</v>
       </c>
       <c r="H68" t="n">
-        <v>0.05742509769865393</v>
+        <v>0.481545809813287</v>
       </c>
       <c r="I68" t="n">
-        <v>0.09909909909909909</v>
+        <v>0.3947503860010293</v>
       </c>
       <c r="J68" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="K68" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="L68" t="n">
-        <v>8</v>
+        <v>85</v>
       </c>
       <c r="M68" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="69">
@@ -4142,34 +4142,34 @@
         <v>192</v>
       </c>
       <c r="C69" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D69" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E69" t="n">
         <v>0</v>
       </c>
       <c r="F69" t="n">
-        <v>0.078125</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="G69" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.4050046339202966</v>
       </c>
       <c r="H69" t="n">
-        <v>0.07783326096396005</v>
+        <v>0.4554928354320452</v>
       </c>
       <c r="I69" t="n">
-        <v>0.1331417624521073</v>
+        <v>0.3687344913151365</v>
       </c>
       <c r="J69" t="n">
-        <v>6</v>
+        <v>77</v>
       </c>
       <c r="K69" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L69" t="n">
-        <v>8</v>
+        <v>89</v>
       </c>
       <c r="M69" t="n">
         <v>9</v>
@@ -4185,37 +4185,37 @@
         <v>192</v>
       </c>
       <c r="C70" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D70" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E70" t="n">
         <v>0</v>
       </c>
       <c r="F70" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.4427083333333333</v>
       </c>
       <c r="G70" t="n">
-        <v>0.5641025641025641</v>
+        <v>0.4901162790697675</v>
       </c>
       <c r="H70" t="n">
-        <v>0.08201613794628054</v>
+        <v>0.4962418481264508</v>
       </c>
       <c r="I70" t="n">
-        <v>0.1431451612903226</v>
+        <v>0.3754673962608299</v>
       </c>
       <c r="J70" t="n">
-        <v>6</v>
+        <v>74</v>
       </c>
       <c r="K70" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="L70" t="n">
-        <v>7</v>
+        <v>98</v>
       </c>
       <c r="M70" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="71">
@@ -4228,37 +4228,37 @@
         <v>192</v>
       </c>
       <c r="C71" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D71" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E71" t="n">
         <v>0</v>
       </c>
       <c r="F71" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.46875</v>
       </c>
       <c r="G71" t="n">
-        <v>0.4769736842105263</v>
+        <v>0.4618312963334001</v>
       </c>
       <c r="H71" t="n">
-        <v>0.07168458781362007</v>
+        <v>0.4793092212447052</v>
       </c>
       <c r="I71" t="n">
-        <v>0.1229233092800805</v>
+        <v>0.4069049061175045</v>
       </c>
       <c r="J71" t="n">
-        <v>3</v>
+        <v>76</v>
       </c>
       <c r="K71" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L71" t="n">
-        <v>5</v>
+        <v>85</v>
       </c>
       <c r="M71" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
     </row>
     <row r="72">
@@ -4271,37 +4271,37 @@
         <v>192</v>
       </c>
       <c r="C72" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D72" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E72" t="n">
         <v>0</v>
       </c>
       <c r="F72" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5572916666666666</v>
       </c>
       <c r="G72" t="n">
-        <v>0.5273109243697479</v>
+        <v>0.5623809523809524</v>
       </c>
       <c r="H72" t="n">
-        <v>0.08301599390708302</v>
+        <v>0.5427592209770428</v>
       </c>
       <c r="I72" t="n">
-        <v>0.1430756843800322</v>
+        <v>0.5111284186562022</v>
       </c>
       <c r="J72" t="n">
-        <v>9</v>
+        <v>83</v>
       </c>
       <c r="K72" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="L72" t="n">
-        <v>5</v>
+        <v>67</v>
       </c>
       <c r="M72" t="n">
-        <v>7</v>
+        <v>24</v>
       </c>
     </row>
     <row r="73">
@@ -4314,37 +4314,37 @@
         <v>192</v>
       </c>
       <c r="C73" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D73" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E73" t="n">
         <v>0</v>
       </c>
       <c r="F73" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G73" t="n">
-        <v>0.5025641025641026</v>
+        <v>0.4325750682438581</v>
       </c>
       <c r="H73" t="n">
-        <v>0.0735632183908046</v>
+        <v>0.4594417077175698</v>
       </c>
       <c r="I73" t="n">
-        <v>0.1279494848786973</v>
+        <v>0.4113377549743462</v>
       </c>
       <c r="J73" t="n">
-        <v>7</v>
+        <v>82</v>
       </c>
       <c r="K73" t="n">
-        <v>8</v>
+        <v>23</v>
       </c>
       <c r="L73" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="M73" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="74">
@@ -4357,37 +4357,37 @@
         <v>192</v>
       </c>
       <c r="C74" t="n">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="D74" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E74" t="n">
         <v>0</v>
       </c>
       <c r="F74" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="G74" t="n">
-        <v>0.5119047619047619</v>
+        <v>0.5083410565338276</v>
       </c>
       <c r="H74" t="n">
-        <v>0.08664021164021163</v>
+        <v>0.503968253968254</v>
       </c>
       <c r="I74" t="n">
-        <v>0.1477713178294573</v>
+        <v>0.4039402985074627</v>
       </c>
       <c r="J74" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="K74" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L74" t="n">
-        <v>6</v>
+        <v>93</v>
       </c>
       <c r="M74" t="n">
-        <v>11</v>
+        <v>15</v>
       </c>
     </row>
     <row r="75">
@@ -4400,37 +4400,37 @@
         <v>192</v>
       </c>
       <c r="C75" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D75" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E75" t="n">
         <v>0</v>
       </c>
       <c r="F75" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.453125</v>
       </c>
       <c r="G75" t="n">
-        <v>0.4375</v>
+        <v>0.3755792400370713</v>
       </c>
       <c r="H75" t="n">
-        <v>0.0689149560117302</v>
+        <v>0.4416748126425546</v>
       </c>
       <c r="I75" t="n">
-        <v>0.116532958398809</v>
+        <v>0.3607103218645948</v>
       </c>
       <c r="J75" t="n">
-        <v>3</v>
+        <v>80</v>
       </c>
       <c r="K75" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L75" t="n">
-        <v>5</v>
+        <v>86</v>
       </c>
       <c r="M75" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="76">
@@ -4443,37 +4443,37 @@
         <v>192</v>
       </c>
       <c r="C76" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D76" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E76" t="n">
         <v>0</v>
       </c>
       <c r="F76" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G76" t="n">
-        <v>0.4558823529411765</v>
+        <v>0.5344919786096256</v>
       </c>
       <c r="H76" t="n">
-        <v>0.07298794395568589</v>
+        <v>0.5140110785272076</v>
       </c>
       <c r="I76" t="n">
-        <v>0.1257653883338704</v>
+        <v>0.4352028446743171</v>
       </c>
       <c r="J76" t="n">
-        <v>7</v>
+        <v>89</v>
       </c>
       <c r="K76" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L76" t="n">
-        <v>10</v>
+        <v>81</v>
       </c>
       <c r="M76" t="n">
-        <v>7</v>
+        <v>12</v>
       </c>
     </row>
     <row r="77">
@@ -4486,37 +4486,37 @@
         <v>192</v>
       </c>
       <c r="C77" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D77" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E77" t="n">
         <v>0</v>
       </c>
       <c r="F77" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.5104166666666666</v>
       </c>
       <c r="G77" t="n">
-        <v>0.5504201680672269</v>
+        <v>0.5132219166490375</v>
       </c>
       <c r="H77" t="n">
-        <v>0.08860553445469344</v>
+        <v>0.5067824199674443</v>
       </c>
       <c r="I77" t="n">
-        <v>0.1524292149292149</v>
+        <v>0.4401985111662531</v>
       </c>
       <c r="J77" t="n">
-        <v>8</v>
+        <v>83</v>
       </c>
       <c r="K77" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L77" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="M77" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
     <row r="78">
@@ -4529,37 +4529,37 @@
         <v>192</v>
       </c>
       <c r="C78" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D78" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E78" t="n">
         <v>0</v>
       </c>
       <c r="F78" t="n">
-        <v>0.109375</v>
+        <v>0.578125</v>
       </c>
       <c r="G78" t="n">
-        <v>0.65625</v>
+        <v>0.5457317073170731</v>
       </c>
       <c r="H78" t="n">
-        <v>0.1079412746079413</v>
+        <v>0.5233566900233566</v>
       </c>
       <c r="I78" t="n">
-        <v>0.1848364315285332</v>
+        <v>0.4811676396997498</v>
       </c>
       <c r="J78" t="n">
-        <v>13</v>
+        <v>97</v>
       </c>
       <c r="K78" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="L78" t="n">
-        <v>3</v>
+        <v>67</v>
       </c>
       <c r="M78" t="n">
-        <v>8</v>
+        <v>14</v>
       </c>
     </row>
     <row r="79">
@@ -4572,37 +4572,37 @@
         <v>192</v>
       </c>
       <c r="C79" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D79" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E79" t="n">
         <v>0</v>
       </c>
       <c r="F79" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.453125</v>
       </c>
       <c r="G79" t="n">
-        <v>0.5210084033613445</v>
+        <v>0.3919987830848798</v>
       </c>
       <c r="H79" t="n">
-        <v>0.08336951801997394</v>
+        <v>0.4614633087277464</v>
       </c>
       <c r="I79" t="n">
-        <v>0.1435006435006435</v>
+        <v>0.3546528377989052</v>
       </c>
       <c r="J79" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="K79" t="n">
+        <v>13</v>
+      </c>
+      <c r="L79" t="n">
+        <v>92</v>
+      </c>
+      <c r="M79" t="n">
         <v>6</v>
-      </c>
-      <c r="L79" t="n">
-        <v>9</v>
-      </c>
-      <c r="M79" t="n">
-        <v>8</v>
       </c>
     </row>
     <row r="80">
@@ -4615,37 +4615,37 @@
         <v>192</v>
       </c>
       <c r="C80" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D80" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E80" t="n">
         <v>0</v>
       </c>
       <c r="F80" t="n">
-        <v>0.078125</v>
+        <v>0.4322916666666667</v>
       </c>
       <c r="G80" t="n">
-        <v>0.5769230769230769</v>
+        <v>0.4180232558139535</v>
       </c>
       <c r="H80" t="n">
-        <v>0.07733990147783251</v>
+        <v>0.4691297208538587</v>
       </c>
       <c r="I80" t="n">
-        <v>0.136271186440678</v>
+        <v>0.3535752895752896</v>
       </c>
       <c r="J80" t="n">
-        <v>6</v>
+        <v>75</v>
       </c>
       <c r="K80" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="L80" t="n">
-        <v>7</v>
+        <v>97</v>
       </c>
       <c r="M80" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="81">
@@ -4658,37 +4658,37 @@
         <v>192</v>
       </c>
       <c r="C81" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D81" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E81" t="n">
         <v>0</v>
       </c>
       <c r="F81" t="n">
-        <v>0.0625</v>
+        <v>0.4635416666666667</v>
       </c>
       <c r="G81" t="n">
-        <v>0.40625</v>
+        <v>0.457266765390311</v>
       </c>
       <c r="H81" t="n">
-        <v>0.06217391304347826</v>
+        <v>0.4780434782608696</v>
       </c>
       <c r="I81" t="n">
-        <v>0.1076998050682261</v>
+        <v>0.3988144094847241</v>
       </c>
       <c r="J81" t="n">
-        <v>5</v>
+        <v>76</v>
       </c>
       <c r="K81" t="n">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="L81" t="n">
-        <v>11</v>
+        <v>87</v>
       </c>
       <c r="M81" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
     </row>
     <row r="82">
@@ -4701,37 +4701,37 @@
         <v>192</v>
       </c>
       <c r="C82" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D82" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E82" t="n">
         <v>0</v>
       </c>
       <c r="F82" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="G82" t="n">
-        <v>0.3206521739130435</v>
+        <v>0.4827160493827161</v>
       </c>
       <c r="H82" t="n">
-        <v>0.05357142857142857</v>
+        <v>0.4907407407407408</v>
       </c>
       <c r="I82" t="n">
-        <v>0.09044142051111849</v>
+        <v>0.4004948745139625</v>
       </c>
       <c r="J82" t="n">
-        <v>2</v>
+        <v>70</v>
       </c>
       <c r="K82" t="n">
         <v>14</v>
       </c>
       <c r="L82" t="n">
-        <v>6</v>
+        <v>92</v>
       </c>
       <c r="M82" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
     </row>
     <row r="83">
@@ -4744,37 +4744,37 @@
         <v>192</v>
       </c>
       <c r="C83" t="n">
-        <v>26</v>
+        <v>192</v>
       </c>
       <c r="D83" t="n">
-        <v>166</v>
+        <v>0</v>
       </c>
       <c r="E83" t="n">
         <v>0</v>
       </c>
       <c r="F83" t="n">
-        <v>0.0625</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4615384615384616</v>
+        <v>0.4929577464788732</v>
       </c>
       <c r="H83" t="n">
-        <v>0.06274424663482414</v>
+        <v>0.4945722970039079</v>
       </c>
       <c r="I83" t="n">
-        <v>0.1104656057927086</v>
+        <v>0.4612918002748512</v>
       </c>
       <c r="J83" t="n">
-        <v>7</v>
+        <v>69</v>
       </c>
       <c r="K83" t="n">
-        <v>8</v>
+        <v>25</v>
       </c>
       <c r="L83" t="n">
-        <v>6</v>
+        <v>73</v>
       </c>
       <c r="M83" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
     </row>
     <row r="84">
@@ -4787,37 +4787,37 @@
         <v>192</v>
       </c>
       <c r="C84" t="n">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="D84" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="E84" t="n">
         <v>0</v>
       </c>
       <c r="F84" t="n">
-        <v>0.1197916666666667</v>
+        <v>0.5052083333333334</v>
       </c>
       <c r="G84" t="n">
-        <v>0.6800699300699301</v>
+        <v>0.4586236933797909</v>
       </c>
       <c r="H84" t="n">
-        <v>0.1215773971855569</v>
+        <v>0.4792734809643285</v>
       </c>
       <c r="I84" t="n">
-        <v>0.2033240136688413</v>
+        <v>0.4161144722942476</v>
       </c>
       <c r="J84" t="n">
-        <v>10</v>
+        <v>86</v>
       </c>
       <c r="K84" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="L84" t="n">
-        <v>3</v>
+        <v>78</v>
       </c>
       <c r="M84" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
     </row>
     <row r="85">
@@ -4830,37 +4830,37 @@
         <v>192</v>
       </c>
       <c r="C85" t="n">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="D85" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="E85" t="n">
         <v>0</v>
       </c>
       <c r="F85" t="n">
-        <v>0.08854166666666667</v>
+        <v>0.5572916666666666</v>
       </c>
       <c r="G85" t="n">
-        <v>0.5</v>
+        <v>0.5339506172839505</v>
       </c>
       <c r="H85" t="n">
-        <v>0.09153380978559647</v>
+        <v>0.5181418361737218</v>
       </c>
       <c r="I85" t="n">
-        <v>0.1530893349075167</v>
+        <v>0.4724422175529336</v>
       </c>
       <c r="J85" t="n">
-        <v>7</v>
+        <v>92</v>
       </c>
       <c r="K85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="L85" t="n">
-        <v>7</v>
+        <v>70</v>
       </c>
       <c r="M85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
     <row r="86">
@@ -4873,37 +4873,37 @@
         <v>192</v>
       </c>
       <c r="C86" t="n">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="D86" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E86" t="n">
         <v>0</v>
       </c>
       <c r="F86" t="n">
-        <v>0.078125</v>
+        <v>0.53125</v>
       </c>
       <c r="G86" t="n">
-        <v>0.4692307692307692</v>
+        <v>0.5254918552993442</v>
       </c>
       <c r="H86" t="n">
-        <v>0.07860950930257862</v>
+        <v>0.5131106517245131</v>
       </c>
       <c r="I86" t="n">
-        <v>0.1334755808440019</v>
+        <v>0.4545454545454546</v>
       </c>
       <c r="J86" t="n">
-        <v>7</v>
+        <v>87</v>
       </c>
       <c r="K86" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="L86" t="n">
-        <v>6</v>
+        <v>76</v>
       </c>
       <c r="M86" t="n">
-        <v>8</v>
+        <v>15</v>
       </c>
     </row>
     <row r="87">
@@ -4916,37 +4916,37 @@
         <v>192</v>
       </c>
       <c r="C87" t="n">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="D87" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="E87" t="n">
         <v>0</v>
       </c>
       <c r="F87" t="n">
-        <v>0.09895833333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G87" t="n">
-        <v>0.6022727272727273</v>
+        <v>0.4972793629727936</v>
       </c>
       <c r="H87" t="n">
-        <v>0.09902333152468801</v>
+        <v>0.4977753662506783</v>
       </c>
       <c r="I87" t="n">
-        <v>0.168038892809535</v>
+        <v>0.4748717948717949</v>
       </c>
       <c r="J87" t="n">
-        <v>9</v>
+        <v>69</v>
       </c>
       <c r="K87" t="n">
-        <v>12</v>
+        <v>28</v>
       </c>
       <c r="L87" t="n">
-        <v>3</v>
+        <v>68</v>
       </c>
       <c r="M87" t="n">
-        <v>10</v>
+        <v>27</v>
       </c>
     </row>
     <row r="88">
@@ -4959,37 +4959,37 @@
         <v>192</v>
       </c>
       <c r="C88" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D88" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E88" t="n">
         <v>0</v>
       </c>
       <c r="F88" t="n">
-        <v>0.06770833333333333</v>
+        <v>0.5208333333333334</v>
       </c>
       <c r="G88" t="n">
-        <v>0.4642857142857143</v>
+        <v>0.5088031012760459</v>
       </c>
       <c r="H88" t="n">
-        <v>0.06816450875856817</v>
+        <v>0.5059297138505059</v>
       </c>
       <c r="I88" t="n">
-        <v>0.1188405797101449</v>
+        <v>0.468975468975469</v>
       </c>
       <c r="J88" t="n">
-        <v>6</v>
+        <v>80</v>
       </c>
       <c r="K88" t="n">
-        <v>7</v>
+        <v>21</v>
       </c>
       <c r="L88" t="n">
-        <v>8</v>
+        <v>71</v>
       </c>
       <c r="M88" t="n">
-        <v>7</v>
+        <v>20</v>
       </c>
     </row>
     <row r="89">
@@ -5002,37 +5002,37 @@
         <v>192</v>
       </c>
       <c r="C89" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D89" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E89" t="n">
         <v>0</v>
       </c>
       <c r="F89" t="n">
-        <v>0.078125</v>
+        <v>0.5</v>
       </c>
       <c r="G89" t="n">
-        <v>0.5050505050505051</v>
+        <v>0.4710472920243484</v>
       </c>
       <c r="H89" t="n">
-        <v>0.08045161994109305</v>
+        <v>0.4797643722046471</v>
       </c>
       <c r="I89" t="n">
-        <v>0.1347329472329472</v>
+        <v>0.4458874458874459</v>
       </c>
       <c r="J89" t="n">
-        <v>5</v>
+        <v>78</v>
       </c>
       <c r="K89" t="n">
-        <v>12</v>
+        <v>25</v>
       </c>
       <c r="L89" t="n">
-        <v>4</v>
+        <v>71</v>
       </c>
       <c r="M89" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="90">
@@ -5045,37 +5045,37 @@
         <v>192</v>
       </c>
       <c r="C90" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D90" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E90" t="n">
         <v>0</v>
       </c>
       <c r="F90" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.5</v>
       </c>
       <c r="G90" t="n">
-        <v>0.4423076923076923</v>
+        <v>0.475</v>
       </c>
       <c r="H90" t="n">
-        <v>0.07391304347826087</v>
+        <v>0.4860869565217391</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1260659694288013</v>
+        <v>0.428287841191067</v>
       </c>
       <c r="J90" t="n">
-        <v>5</v>
+        <v>82</v>
       </c>
       <c r="K90" t="n">
-        <v>9</v>
+        <v>18</v>
       </c>
       <c r="L90" t="n">
-        <v>8</v>
+        <v>78</v>
       </c>
       <c r="M90" t="n">
-        <v>9</v>
+        <v>14</v>
       </c>
     </row>
     <row r="91">
@@ -5088,37 +5088,37 @@
         <v>192</v>
       </c>
       <c r="C91" t="n">
-        <v>31</v>
+        <v>192</v>
       </c>
       <c r="D91" t="n">
-        <v>161</v>
+        <v>0</v>
       </c>
       <c r="E91" t="n">
         <v>0</v>
       </c>
       <c r="F91" t="n">
-        <v>0.09895833333333333</v>
+        <v>0.5885416666666666</v>
       </c>
       <c r="G91" t="n">
-        <v>0.6239316239316239</v>
+        <v>0.6110627177700348</v>
       </c>
       <c r="H91" t="n">
-        <v>0.1003284072249589</v>
+        <v>0.5558292282430214</v>
       </c>
       <c r="I91" t="n">
-        <v>0.1715092816787732</v>
+        <v>0.50968159043155</v>
       </c>
       <c r="J91" t="n">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="K91" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="L91" t="n">
-        <v>4</v>
+        <v>69</v>
       </c>
       <c r="M91" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
     </row>
     <row r="92">
@@ -5131,37 +5131,37 @@
         <v>192</v>
       </c>
       <c r="C92" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D92" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
         <v>0</v>
       </c>
       <c r="F92" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.546875</v>
       </c>
       <c r="G92" t="n">
-        <v>0.3798076923076923</v>
+        <v>0.5195286195286195</v>
       </c>
       <c r="H92" t="n">
-        <v>0.05846862659060992</v>
+        <v>0.5095436594997806</v>
       </c>
       <c r="I92" t="n">
-        <v>0.1008403361344538</v>
+        <v>0.454527642621559</v>
       </c>
       <c r="J92" t="n">
-        <v>5</v>
+        <v>92</v>
       </c>
       <c r="K92" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L92" t="n">
-        <v>8</v>
+        <v>73</v>
       </c>
       <c r="M92" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="93">
@@ -5174,37 +5174,37 @@
         <v>192</v>
       </c>
       <c r="C93" t="n">
-        <v>32</v>
+        <v>192</v>
       </c>
       <c r="D93" t="n">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="E93" t="n">
         <v>0</v>
       </c>
       <c r="F93" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.5</v>
       </c>
       <c r="G93" t="n">
-        <v>0.5324675324675324</v>
+        <v>0.4457912457912458</v>
       </c>
       <c r="H93" t="n">
-        <v>0.08454238027708083</v>
+        <v>0.4736555034362386</v>
       </c>
       <c r="I93" t="n">
-        <v>0.1432216905901116</v>
+        <v>0.4071024189397839</v>
       </c>
       <c r="J93" t="n">
-        <v>7</v>
+        <v>86</v>
       </c>
       <c r="K93" t="n">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="L93" t="n">
-        <v>4</v>
+        <v>79</v>
       </c>
       <c r="M93" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="94">
@@ -5217,37 +5217,37 @@
         <v>192</v>
       </c>
       <c r="C94" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D94" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
         <v>0</v>
       </c>
       <c r="F94" t="n">
-        <v>0.07291666666666667</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G94" t="n">
-        <v>0.4772727272727273</v>
+        <v>0.5006974716652136</v>
       </c>
       <c r="H94" t="n">
-        <v>0.07517482517482518</v>
+        <v>0.5004370629370629</v>
       </c>
       <c r="I94" t="n">
-        <v>0.1283839212469237</v>
+        <v>0.4603243243243244</v>
       </c>
       <c r="J94" t="n">
-        <v>5</v>
+        <v>84</v>
       </c>
       <c r="K94" t="n">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="L94" t="n">
-        <v>6</v>
+        <v>71</v>
       </c>
       <c r="M94" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="95">
@@ -5260,37 +5260,37 @@
         <v>192</v>
       </c>
       <c r="C95" t="n">
-        <v>33</v>
+        <v>192</v>
       </c>
       <c r="D95" t="n">
-        <v>159</v>
+        <v>0</v>
       </c>
       <c r="E95" t="n">
         <v>0</v>
       </c>
       <c r="F95" t="n">
-        <v>0.09375</v>
+        <v>0.4895833333333333</v>
       </c>
       <c r="G95" t="n">
-        <v>0.5582706766917294</v>
+        <v>0.4829059829059829</v>
       </c>
       <c r="H95" t="n">
-        <v>0.09375</v>
+        <v>0.4895833333333334</v>
       </c>
       <c r="I95" t="n">
-        <v>0.1600790513833992</v>
+        <v>0.4343434343434343</v>
       </c>
       <c r="J95" t="n">
-        <v>9</v>
+        <v>77</v>
       </c>
       <c r="K95" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="L95" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="M95" t="n">
-        <v>9</v>
+        <v>17</v>
       </c>
     </row>
     <row r="96">
@@ -5303,37 +5303,37 @@
         <v>192</v>
       </c>
       <c r="C96" t="n">
-        <v>30</v>
+        <v>192</v>
       </c>
       <c r="D96" t="n">
-        <v>162</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
         <v>0</v>
       </c>
       <c r="F96" t="n">
-        <v>0.0625</v>
+        <v>0.4739583333333333</v>
       </c>
       <c r="G96" t="n">
-        <v>0.4</v>
+        <v>0.4684394071490846</v>
       </c>
       <c r="H96" t="n">
-        <v>0.06274424663482414</v>
+        <v>0.4803517151541468</v>
       </c>
       <c r="I96" t="n">
-        <v>0.108467971096858</v>
+        <v>0.4231146809460062</v>
       </c>
       <c r="J96" t="n">
-        <v>7</v>
+        <v>74</v>
       </c>
       <c r="K96" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="L96" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="M96" t="n">
-        <v>5</v>
+        <v>17</v>
       </c>
     </row>
     <row r="97">
@@ -5346,37 +5346,37 @@
         <v>192</v>
       </c>
       <c r="C97" t="n">
-        <v>28</v>
+        <v>192</v>
       </c>
       <c r="D97" t="n">
-        <v>164</v>
+        <v>0</v>
       </c>
       <c r="E97" t="n">
         <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0.1041666666666667</v>
+        <v>0.5260416666666666</v>
       </c>
       <c r="G97" t="n">
-        <v>0.7602339181286549</v>
+        <v>0.5577472841623785</v>
       </c>
       <c r="H97" t="n">
-        <v>0.1037776812852801</v>
+        <v>0.5328918801563178</v>
       </c>
       <c r="I97" t="n">
-        <v>0.1802340054767239</v>
+        <v>0.4728298584919893</v>
       </c>
       <c r="J97" t="n">
-        <v>8</v>
+        <v>81</v>
       </c>
       <c r="K97" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="L97" t="n">
-        <v>1</v>
+        <v>78</v>
       </c>
       <c r="M97" t="n">
-        <v>12</v>
+        <v>20</v>
       </c>
     </row>
     <row r="98">
@@ -5389,37 +5389,37 @@
         <v>192</v>
       </c>
       <c r="C98" t="n">
-        <v>27</v>
+        <v>192</v>
       </c>
       <c r="D98" t="n">
-        <v>165</v>
+        <v>0</v>
       </c>
       <c r="E98" t="n">
         <v>0</v>
       </c>
       <c r="F98" t="n">
-        <v>0.05729166666666666</v>
+        <v>0.4427083333333333</v>
       </c>
       <c r="G98" t="n">
-        <v>0.3647058823529412</v>
+        <v>0.4308229320922361</v>
       </c>
       <c r="H98" t="n">
-        <v>0.05522875816993465</v>
+        <v>0.4643790849673203</v>
       </c>
       <c r="I98" t="n">
-        <v>0.09563025210084034</v>
+        <v>0.3801406028422291</v>
       </c>
       <c r="J98" t="n">
-        <v>2</v>
+        <v>73</v>
       </c>
       <c r="K98" t="n">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="L98" t="n">
-        <v>8</v>
+        <v>90</v>
       </c>
       <c r="M98" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
     </row>
     <row r="99">
@@ -5432,37 +5432,37 @@
         <v>192</v>
       </c>
       <c r="C99" t="n">
-        <v>29</v>
+        <v>192</v>
       </c>
       <c r="D99" t="n">
-        <v>163</v>
+        <v>0</v>
       </c>
       <c r="E99" t="n">
         <v>0</v>
       </c>
       <c r="F99" t="n">
-        <v>0.0625</v>
+        <v>0.5416666666666666</v>
       </c>
       <c r="G99" t="n">
-        <v>0.4166666666666666</v>
+        <v>0.5421292083712466</v>
       </c>
       <c r="H99" t="n">
-        <v>0.06212599281906213</v>
+        <v>0.5251876836035252</v>
       </c>
       <c r="I99" t="n">
-        <v>0.108039376538146</v>
+        <v>0.4802510151347361</v>
       </c>
       <c r="J99" t="n">
-        <v>7</v>
+        <v>85</v>
       </c>
       <c r="K99" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="L99" t="n">
-        <v>7</v>
+        <v>72</v>
       </c>
       <c r="M99" t="n">
-        <v>5</v>
+        <v>19</v>
       </c>
     </row>
     <row r="100">
@@ -5475,37 +5475,37 @@
         <v>192</v>
       </c>
       <c r="C100" t="n">
-        <v>35</v>
+        <v>192</v>
       </c>
       <c r="D100" t="n">
-        <v>157</v>
+        <v>0</v>
       </c>
       <c r="E100" t="n">
         <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.09895833333333333</v>
+        <v>0.4479166666666667</v>
       </c>
       <c r="G100" t="n">
-        <v>0.5408496732026145</v>
+        <v>0.4147727272727273</v>
       </c>
       <c r="H100" t="n">
-        <v>0.09836601307189544</v>
+        <v>0.4738562091503268</v>
       </c>
       <c r="I100" t="n">
-        <v>0.1664330218068536</v>
+        <v>0.3515993373263667</v>
       </c>
       <c r="J100" t="n">
-        <v>8</v>
+        <v>80</v>
       </c>
       <c r="K100" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="L100" t="n">
-        <v>9</v>
+        <v>96</v>
       </c>
       <c r="M100" t="n">
-        <v>11</v>
+        <v>6</v>
       </c>
     </row>
     <row r="101">
@@ -5518,37 +5518,37 @@
         <v>192</v>
       </c>
       <c r="C101" t="n">
-        <v>34</v>
+        <v>192</v>
       </c>
       <c r="D101" t="n">
-        <v>158</v>
+        <v>0</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="n">
-        <v>0.08333333333333333</v>
+        <v>0.515625</v>
       </c>
       <c r="G101" t="n">
-        <v>0.4901185770750988</v>
+        <v>0.5162894013116142</v>
       </c>
       <c r="H101" t="n">
-        <v>0.08380373425966131</v>
+        <v>0.5083586626139818</v>
       </c>
       <c r="I101" t="n">
-        <v>0.1405159570297185</v>
+        <v>0.4437902999719652</v>
       </c>
       <c r="J101" t="n">
-        <v>6</v>
+        <v>84</v>
       </c>
       <c r="K101" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L101" t="n">
-        <v>5</v>
+        <v>79</v>
       </c>
       <c r="M101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -5584,10 +5584,10 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>653</v>
+        <v>8084</v>
       </c>
       <c r="C2" t="n">
-        <v>933</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="3">
@@ -5597,10 +5597,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>657</v>
+        <v>8193</v>
       </c>
       <c r="C3" t="n">
-        <v>919</v>
+        <v>1453</v>
       </c>
     </row>
   </sheetData>
@@ -5651,16 +5651,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>13</v>
+        <v>268</v>
       </c>
       <c r="C2" t="n">
-        <v>53</v>
+        <v>119</v>
       </c>
       <c r="D2" t="n">
-        <v>13</v>
+        <v>295</v>
       </c>
       <c r="E2" t="n">
-        <v>47</v>
+        <v>118</v>
       </c>
     </row>
     <row r="3">
@@ -5670,16 +5670,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>20</v>
+        <v>318</v>
       </c>
       <c r="C3" t="n">
-        <v>51</v>
+        <v>86</v>
       </c>
       <c r="D3" t="n">
-        <v>17</v>
+        <v>312</v>
       </c>
       <c r="E3" t="n">
-        <v>55</v>
+        <v>84</v>
       </c>
     </row>
     <row r="4">
@@ -5689,16 +5689,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>30</v>
+        <v>584</v>
       </c>
       <c r="C4" t="n">
-        <v>106</v>
+        <v>237</v>
       </c>
       <c r="D4" t="n">
-        <v>44</v>
+        <v>566</v>
       </c>
       <c r="E4" t="n">
-        <v>108</v>
+        <v>213</v>
       </c>
     </row>
     <row r="5">
@@ -5708,16 +5708,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>59</v>
+        <v>709</v>
       </c>
       <c r="C5" t="n">
-        <v>56</v>
+        <v>96</v>
       </c>
       <c r="D5" t="n">
-        <v>62</v>
+        <v>702</v>
       </c>
       <c r="E5" t="n">
-        <v>67</v>
+        <v>93</v>
       </c>
     </row>
     <row r="6">
@@ -5727,16 +5727,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>68</v>
+        <v>728</v>
       </c>
       <c r="C6" t="n">
-        <v>76</v>
+        <v>93</v>
       </c>
       <c r="D6" t="n">
-        <v>59</v>
+        <v>691</v>
       </c>
       <c r="E6" t="n">
-        <v>65</v>
+        <v>88</v>
       </c>
     </row>
     <row r="7">
@@ -5746,16 +5746,16 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82</v>
+        <v>682</v>
       </c>
       <c r="C7" t="n">
-        <v>44</v>
+        <v>58</v>
       </c>
       <c r="D7" t="n">
-        <v>92</v>
+        <v>792</v>
       </c>
       <c r="E7" t="n">
-        <v>42</v>
+        <v>68</v>
       </c>
     </row>
     <row r="8">
@@ -5765,16 +5765,16 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>82</v>
+        <v>755</v>
       </c>
       <c r="C8" t="n">
-        <v>55</v>
+        <v>14</v>
       </c>
       <c r="D8" t="n">
-        <v>69</v>
+        <v>817</v>
       </c>
       <c r="E8" t="n">
-        <v>65</v>
+        <v>14</v>
       </c>
     </row>
     <row r="9">
@@ -5784,16 +5784,16 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>60</v>
+        <v>714</v>
       </c>
       <c r="C9" t="n">
-        <v>71</v>
+        <v>108</v>
       </c>
       <c r="D9" t="n">
-        <v>67</v>
+        <v>677</v>
       </c>
       <c r="E9" t="n">
-        <v>64</v>
+        <v>101</v>
       </c>
     </row>
     <row r="10">
@@ -5803,16 +5803,16 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>83</v>
+        <v>767</v>
       </c>
       <c r="C10" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="D10" t="n">
-        <v>86</v>
+        <v>755</v>
       </c>
       <c r="E10" t="n">
-        <v>34</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
@@ -5822,16 +5822,16 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>39</v>
+        <v>678</v>
       </c>
       <c r="C11" t="n">
-        <v>97</v>
+        <v>134</v>
       </c>
       <c r="D11" t="n">
-        <v>36</v>
+        <v>675</v>
       </c>
       <c r="E11" t="n">
-        <v>74</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -5841,16 +5841,16 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>50</v>
+        <v>653</v>
       </c>
       <c r="C12" t="n">
-        <v>90</v>
+        <v>135</v>
       </c>
       <c r="D12" t="n">
-        <v>41</v>
+        <v>661</v>
       </c>
       <c r="E12" t="n">
-        <v>74</v>
+        <v>151</v>
       </c>
     </row>
     <row r="13">
@@ -5860,16 +5860,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>37</v>
+        <v>667</v>
       </c>
       <c r="C13" t="n">
-        <v>82</v>
+        <v>146</v>
       </c>
       <c r="D13" t="n">
-        <v>48</v>
+        <v>644</v>
       </c>
       <c r="E13" t="n">
-        <v>93</v>
+        <v>143</v>
       </c>
     </row>
     <row r="14">
@@ -5879,16 +5879,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>30</v>
+        <v>561</v>
       </c>
       <c r="C14" t="n">
-        <v>120</v>
+        <v>207</v>
       </c>
       <c r="D14" t="n">
-        <v>23</v>
+        <v>606</v>
       </c>
       <c r="E14" t="n">
-        <v>131</v>
+        <v>226</v>
       </c>
     </row>
   </sheetData>
